--- a/mosip_master/xlsx/reg_working_nonworking.xlsx
+++ b/mosip_master/xlsx/reg_working_nonworking.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chith\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571835AF-AED9-40C6-BFE8-036FD9494A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD91DE97-99D3-431D-A326-4AB315BF5986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="9">
   <si>
     <t>lang_code</t>
   </si>
@@ -49,12 +49,6 @@
   </si>
   <si>
     <t>TRUE</t>
-  </si>
-  <si>
-    <t>tam</t>
-  </si>
-  <si>
-    <t>sin</t>
   </si>
   <si>
     <t>10000</t>
@@ -450,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -482,7 +476,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>101</v>
@@ -499,7 +493,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>102</v>
@@ -516,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>103</v>
@@ -533,7 +527,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>104</v>
@@ -550,7 +544,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <v>105</v>
@@ -567,7 +561,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>106</v>
@@ -584,7 +578,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>107</v>
@@ -596,273 +590,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1">
-        <v>101</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1">
-        <v>102</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>103</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1">
-        <v>104</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1">
-        <v>105</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1">
-        <v>106</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1">
-        <v>107</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1">
-        <v>101</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1">
-        <v>102</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1">
-        <v>103</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="1">
-        <v>104</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="1">
-        <v>105</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1">
-        <v>106</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="1">
-        <v>107</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D55" s="4"/>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D56" s="4"/>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D73" s="4"/>
-    </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D77" s="4"/>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="4"/>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D63" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
